--- a/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_r2/staggered_7d/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/threshold_0.9/window_15/return_r2/staggered_7d/next_day_vwap/next_day_vwap_backtest_metrics.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'performance'!$A$1:$C$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'parameters'!$A$1:$C$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'parameters'!$A$1:$C$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1.079445268014304</v>
+        <v>1.197372597423207</v>
       </c>
     </row>
     <row r="6">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.07944526801429563</v>
+        <v>0.1973725974232157</v>
       </c>
     </row>
     <row r="7">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.01459015787032314</v>
+        <v>0.03471893475355614</v>
       </c>
     </row>
     <row r="8">
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.03196004351872905</v>
+        <v>0.05243342708870058</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.3058944529381822</v>
+        <v>0.2546247132125279</v>
       </c>
     </row>
     <row r="11">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1513540691247463</v>
+        <v>0.2026663637325317</v>
       </c>
     </row>
     <row r="12">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2193803477042617</v>
+        <v>0.2921675113145452</v>
       </c>
     </row>
     <row r="13">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5656246048682771</v>
+        <v>0.5512170029625899</v>
       </c>
     </row>
     <row r="14">
@@ -721,7 +721,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.02579477226546907</v>
+        <v>0.06298596481413773</v>
       </c>
     </row>
     <row r="16">
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.2111307372526385</v>
+        <v>0.1549638550564021</v>
       </c>
     </row>
     <row r="17">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.2834750328421326</v>
+        <v>0.4204579656417319</v>
       </c>
     </row>
     <row r="18">
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.3497974027352415</v>
+        <v>0.304511579130664</v>
       </c>
     </row>
     <row r="19">
@@ -782,7 +782,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2022年04月-2025年01月</t>
+          <t>2023年06月-2024年09月</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>25.01881963101689</v>
+        <v>26.92491843257795</v>
       </c>
     </row>
     <row r="21">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.09980632673833077</v>
+        <v>0.1074102314224787</v>
       </c>
     </row>
     <row r="22">
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.2328781474561357</v>
+        <v>0.2481624211456381</v>
       </c>
     </row>
     <row r="23">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>6.126315789473685</v>
+        <v>9.527067669172933</v>
       </c>
     </row>
     <row r="24">
@@ -888,7 +888,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="18" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>波动过滤</t>
@@ -1266,11 +1266,13 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>日收益窗口 L</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>20</v>
+          <t>过滤模式</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>保留高波动（high）</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1281,240 +1283,238 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>日收益窗口 L</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>波动过滤</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>价格个数</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C25" s="10" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>波动过滤</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>过滤波动率公式</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>L个简单日收益的样本标准差(ddof=1)；与趋势得分分母独立</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>波动过滤</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>波动率保留比例</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="C27" s="5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>波动过滤</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>波动排名规则</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>当日全体有效代表指数波动降序，保留ceil(指数数×比例)；并列按指数代码升序</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>BIAS过滤</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>BIAS模式</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>BIAS过滤</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>均线窗口 M</t>
         </is>
       </c>
-      <c r="C29" s="10" t="n">
+      <c r="C30" s="10" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>BIAS过滤</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>BIAS公式</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>截至信号日最新指数收盘价÷最近M个收盘价的简单均值−1；均线含最新价格</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>BIAS过滤</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>BIAS下限</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
         <is>
           <t>未启用</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>BIAS过滤</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>BIAS上限</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="C33" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>BIAS过滤</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>通过条件</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>BIAS ≤ 上限</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>过滤数据</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>价格日期</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>只使用不晚于信号日的指数价格；次日VWAP使用原信号日指标</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>过滤数据</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>价格允许滞后（自然日）</t>
         </is>
       </c>
-      <c r="C35" s="10" t="n">
+      <c r="C36" s="10" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>过滤数据</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>缺失历史处理</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>启用的过滤指标历史不足或过期时报错；不缩小波动排名分母</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>ETF选择</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>代表ETF选择</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>跟踪同一指数中当日成交量最大</t>
         </is>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>账户结构</t>
+          <t>ETF选择</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>调仓模式</t>
+          <t>代表ETF选择</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>staggered</t>
+          <t>跟踪同一指数中当日成交量最大</t>
         </is>
       </c>
     </row>
@@ -1526,28 +1526,30 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>调仓模式</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>staggered</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>账户结构</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>组合结构</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>7个独立账户逐日错峰持有7个交易日</t>
         </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>账户结构</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>账户数量</t>
-        </is>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1558,105 +1560,105 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
+          <t>账户数量</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>账户结构</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>每账户初始资金比例</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C42" s="5" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>账户结构</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>计划调仓账户数</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>每个交易日1个</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>账户结构</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>单账户调仓间隔（交易日）</t>
         </is>
       </c>
-      <c r="C43" s="10" t="n">
+      <c r="C44" s="10" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>账户结构</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>账户之间资金转移</t>
         </is>
       </c>
-      <c r="C44" s="9" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>无；各账户独立复利并保留自己的现金</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>交易设置</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>初始净值 NAV₀</t>
-        </is>
-      </c>
-      <c r="C45" s="10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>收益参数</t>
+          <t>交易设置</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>年化无风险利率 r_f</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="n">
-        <v>0.015</v>
+          <t>初始净值 NAV₀</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>交易成本</t>
+          <t>收益参数</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>买入成本 c_buy</t>
+          <t>年化无风险利率 r_f</t>
         </is>
       </c>
       <c r="C47" s="5" t="n">
-        <v>0.001</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="48">
@@ -1667,7 +1669,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>卖出成本 c_sell</t>
+          <t>买入成本 c_buy</t>
         </is>
       </c>
       <c r="C48" s="5" t="n">
@@ -1682,26 +1684,26 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>完整换仓成本 T_c</t>
+          <t>卖出成本 c_sell</t>
         </is>
       </c>
       <c r="C49" s="5" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>容量参数</t>
+          <t>交易成本</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>当日成交额使用比例 ρ_amt</t>
+          <t>完整换仓成本 T_c</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0.1</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="51">
@@ -1712,11 +1714,11 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>倒序分位 q_desc</t>
+          <t>当日成交额使用比例 ρ_amt</t>
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>0.95</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="52">
@@ -1727,66 +1729,81 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
+          <t>倒序分位 q_desc</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>容量参数</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>等价升序分位 q_asc</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C53" s="5" t="n">
         <v>0.05000000000000004</v>
-      </c>
-    </row>
-    <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>组合约束</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>指数权重</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>过滤后成功匹配n只ETF，每只目标权重1/n；n=0时空仓</t>
-        </is>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>收益口径</t>
+          <t>组合约束</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>扣费后收益</t>
+          <t>指数权重</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>买入和卖出均扣除交易成本</t>
+          <t>过滤后成功匹配n只ETF，每只目标权重1/n；n=0时空仓</t>
         </is>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>收益口径</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>扣费后收益</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>买入和卖出均扣除交易成本</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
           <t>容量口径</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>组合容量</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C56" s="9" t="inlineStr">
         <is>
           <t>各持仓ETF容量的5%分位</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C55"/>
+  <autoFilter ref="A1:C56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>